--- a/Financial Literacy To do List.xlsx
+++ b/Financial Literacy To do List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cebd68c6d368de60/Documentos/GitHub/financial-education-brazil/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_63F44D745B5C5DDA94E9AA3FA741600735BE4DCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C31B8A67-7252-4E0F-9218-71FF89782302}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_69C03E055B4261BB91B54BB7270273B71D7EC03F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53A41659-C38F-4309-984D-4CDE964DB472}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comments" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="195">
   <si>
     <t>To Do</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Como endereçar</t>
   </si>
   <si>
+    <t>Solução aplicada (Pilot)</t>
+  </si>
+  <si>
     <t>Footnote 10 tries to minimize that the data collection method for third graders was very different to that used with other grades. Data for attitudes among the youngest students actually comes from legal guardians who answered “based on how they believed their child would behave in a given situation”. First, the authors do not provide a sense of the response rate of guardians. Presumably, it was lower when compared to other grades (since the questionnaire was sent home to the guardian) and it remains to be seen if it was uncorrelated to treatment status. Second, the responses could be uninformative of students’ attitudes. Even worse, they could be endogenously biased depending on the effect of the treatment on the probability of talking to parents about financial matters. Please evaluate if this sub-sample is worth including in the paper.</t>
   </si>
   <si>
@@ -169,18 +172,31 @@
     <t>Potentially endogenous allocation of participation to specific classrooms within randomly chosen schools since this allocation could differ between treatment and control since treatment requires the teacher to offer a program. You only mention this later in section 2.1 when presenting balancing tests and explaining why you fail balance on the test score variable. This issue needs to be raised up front when describing the experiment with considerably attention paid to issues of internal validity concerns arising from this issue.</t>
   </si>
   <si>
+    <t>Pilot</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Dentro de cada escola sorteada, a alocação a turmas específicas pode ser endógena — em escolas de tratamento a participação depende de o professor topar ensinar. Esse ponto só aparece lá na Seção 2.1, quando explicamos por que falhamos no balance em test scores. O reviewer quer que isso seja trazido pra frente com atenção a validade interna.</t>
+  </si>
+  <si>
+    <t>Mover essa discussão para o início da Seção 2 / desenho experimental e adicionar um parágrafo reconhecendo explicitamente essa fonte de endogeneidade. Mostrar como controlamos (scores passados, estratos), estimar Lee bounds para quantificar viés potencial (liga com row 49) e reportar balance dentro de tratamento entre turmas que aderiram vs. não aderiram.</t>
+  </si>
+  <si>
+    <t>Endereçado no último parágrafo da subseção 2.2 'Sample Selection' (Seção 2 - Pilot). Mudanças:
+• Atendendo ao pedido do reviewer de 'raised up front' (em vez de só no balance test), trouxemos a discussão da alocação endógena de turmas para o desenho experimental, no parágrafo que começa com 'An important feature of the design is that, within each school, the program was not delivered to every class of the pilot grades...'
+• Reconhecemos que a randomização foi preservada APENAS no nível da escola, e que a seleção de uma turma por série dentro de cada escola é potencial fonte de viés.
+• Acrescentamos evidência de balance dos observáveis (Sec. 3 - Data) como argumento de que, embora não-aleatória, essa seleção não produziu diferenças sistemáticas detectáveis no nosso sample.
+• Pendente: examinar formalmente a robustez (ex. Lee bounds) na Seção 6 (Results).</t>
+  </si>
+  <si>
+    <t>Therefore, you really need to emphasize the focus on elementary and middle school students and document carefully the lack of work on financial education in this age group.</t>
+  </si>
+  <si>
     <t>Intro</t>
   </si>
   <si>
-    <t>Dentro de cada escola sorteada, a alocação a turmas específicas pode ser endógena — em escolas de tratamento a participação depende de o professor topar ensinar. Esse ponto só aparece lá na Seção 2.1, quando explicamos por que falhamos no balance em test scores. O reviewer quer que isso seja trazido pra frente com atenção a validade interna.</t>
-  </si>
-  <si>
-    <t>Mover essa discussão para o início da Seção 2 / desenho experimental e adicionar um parágrafo reconhecendo explicitamente essa fonte de endogeneidade. Mostrar como controlamos (scores passados, estratos), estimar Lee bounds para quantificar viés potencial (liga com row 49) e reportar balance dentro de tratamento entre turmas que aderiram vs. não aderiram.</t>
-  </si>
-  <si>
-    <t>Therefore, you really need to emphasize the focus on elementary and middle school students and document carefully the lack of work on financial education in this age group.</t>
-  </si>
-  <si>
     <t>Vivian?</t>
   </si>
   <si>
@@ -421,9 +437,6 @@
     <t>One critical thing that you can do is to describe the specific items in some more detail in the paper to give us a sense of your instrument. Are these items relatively neutral survey questions or do they ask people to make choices in the way an experiment would ask people to make choices, and the only difference is the lack of financial incentive backing up that choice. In the later case, I think that you can make an argument that your lack of financial incentives is not a major issue, and that it was a reasonable design decision in order to obtain a larger sample with more power.</t>
   </si>
   <si>
-    <t>Pilot</t>
-  </si>
-  <si>
     <t>Nao achei esse ponto muito claro. Vamos conversar</t>
   </si>
   <si>
@@ -445,6 +458,16 @@
     <t>Ampliar a Seção 2 substancialmente: (i) resumir o conteúdo dos livros por faixa (tópicos, número de lições, exemplos); (ii) descrever como o material transversal foi distribuído entre disciplinas (ex.: textos para português, problemas para matemática); (iii) descrever o treinamento e o suporte dados aos professores (carga horária, materiais, acompanhamento). Informação a ser levantada junto à AEF-Brasil se necessário (ligado a rows 12, 41, 43).</t>
   </si>
   <si>
+    <t>Endereçado na nova Seção 2 (Pilot), reescrita do zero. Mudanças concretas:
+• Criada subseção 'Teaching Materials' com descrição detalhada do programa.
+• Criada Tabela 1 (tab:materials) com formato pedagógico + conceitos por série do piloto (3, 5, 7, 9), extraída diretamente dos livros do professor.
+• Explicação da definição da OCDE (3 vertentes: information, instruction, objective advice) e por que o programa cobre só as duas primeiras.
+• Listagem dos 6 objetivos e das 10 competências do programa (em footnote, com códigos C01-C10).
+• Descrição da entrega transversal e do papel do professor 'como cidadão e não como especialista de disciplina' (com referência aos livros do professor, Parte I, Seção 4.2).
+• Detalhe dos ícones nas margens do Livro do Professor que sinalizam (i) conexões com Português/Matemática/Educação Ambiental e (ii) introdução de conceitos financeiros e armadilhas psicológicas.
+• OBS: os detalhes operacionais (treinamento dos professores, instruções recebidas, modelo cascata) ficam para a Seção 4 (Implementation).</t>
+  </si>
+  <si>
     <t>It is not clear if the textbooks designed for each group of grades were covered since the beginning of the material in all grades. I imagine that the structure of the textbooks was such that each lesson was building in the previous ones. Section 2 fails to explain if teachers were instructed (or independently decided) to cover each textbook since the beginning of the lessons or there was a different starting point (e.g., lesson number) depending on the grade. I suspect teachers started covering the material since the beginning if this was the first time that students were exposed to financial education material and given the cumulative nature of the textbooks. If so, it would have been better to select the initial grade covered by each textbook._x000D_</t>
   </si>
   <si>
@@ -457,6 +480,12 @@
     <t>Levantar com AEF-Brasil e/ou usar os dados do questionário de professores (se houver pergunta sobre lições efetivamente cobertas). Se a resposta for 'começaram pelo início em todas as séries', reportar isso no texto. Se variou, descrever a variação e controlar por isso onde possível. Alinhado com F41 (resposta não é óbvia).</t>
   </si>
   <si>
+    <t>Endereçado na Seção 4 (Implementation) - comentário tagueado originalmente como Pilot, mas é sobre comportamento do professor em sala, não sobre desenho do material. Status atual:
+• Os livros têm estrutura cumulativa (especialmente 7º ano: 6 encontros com regras que se acumulam), o que sugere que faz pouco sentido começar pelo meio.
+• Faltam dados diretos sobre se os professores começaram pela Lição 1.
+• Pendente: verificar com AEF-Brasil ou usar os dados do questionário de professores (se houver pergunta sobre lições efetivamente cobertas) na reescrita da Seção 4.</t>
+  </si>
+  <si>
     <t>The authors mention that the grade coverage of their intervention allows them to “assess whether the effect of the program varies by school grade and student’ life cycle”. This is not correct. As they themselves mention in footnote 8, the differences across grades could be attributed to differences in the content of the textbooks. More in general, I am not sure if comparing the results across grades is at all relevant since it is not possible to disentangle if differences in impacts are explained by differences in material or differences in students’ age.</t>
   </si>
   <si>
@@ -469,6 +498,13 @@
     <t>Seguir F42: reescrever, sendo mais cauteloso na intro e nos resultados ao comparar séries. Substituir 'life-cycle effects' por 'effects across grades, which conflate age and curriculum differences'. Listar explicitamente essa limitação na seção de discussão e na conclusão.</t>
   </si>
   <si>
+    <t>Endereçado de duas formas na Seção 2:
+• REMOVIDA a frase original do paper que afirmava 'this strategy allows us to assess whether the effect... varies by school grade and student's life cycle' (era exatamente o que o reviewer criticou).
+• ADICIONADO parágrafo explícito (atualmente marcado em vermelho na linha 42 do .tex para revisão final) reconhecendo que entre as 4 séries do piloto variam SIMULTANEAMENTE três dimensões: idade do aluno, conteúdo do livro e método pedagógico (projeto-objeto vs. narrativa).
+• A nova redação: 'Differences in estimated effects across grades therefore cannot be cleanly interpreted as life-cycle or maturation effects, as they also embed differences in the specific content of each volume and in how the content is delivered. We return to this caveat when presenting grade-specific estimates in [Section 6].'
+• Pendente: incluir o caveat também em Results (Seção 6) na hora de discutir os efeitos por série.</t>
+  </si>
+  <si>
     <t>The authors do not provide any information about the content of the textbooks and the characteristics of the lessons imparted. In section 2 they refer the reader to Table A. 1, but these table presents the topics evaluated in the financial literacy test.</t>
   </si>
   <si>
@@ -476,6 +512,13 @@
   </si>
   <si>
     <t>Criar tabela nova (ou melhorar a A.1) com resumo do CONTEÚDO dos livros por série: tópicos principais, número de lições, exemplos de exercícios. Fonte: os próprios livros do programa ENEF/AEF-Brasil (públicos). Incluir no apêndice ou corpo dependendo do tamanho.</t>
+  </si>
+  <si>
+    <t>Endereçado na nova Seção 2 (Pilot):
+• REMOVIDA a referência confusa a 'Table A.1' como fonte do conteúdo dos livros (Table A.1 é sobre os descritores da PROVA, não sobre o material didático).
+• CRIADA Tabela 1 nova (tab:materials) com o conteúdo dos livros do aluno, transcrito do Quadro 2 dos livros do professor para cada série do piloto (3, 5, 7, 9). Inclui formato pedagógico e conceitos centrais.
+• Tabela inclui notas com fonte: 'Based on the student and teacher books, volumes 3, 5, 7, and 9, CONEF (2014). Materials are publicly available on the CVM's investor education portal at https://gmw.investidor.gov.br/ensino-fundamental/'.
+• A descrição literal por projeto/história/encontro/seção está no documento de referência 'Descritores_Material_Didatico.docx' na raiz do repo (criado para o Caio).</t>
   </si>
   <si>
     <t>Describe the degree of two-sided non-compliance, which is mentioned later in the paper without providing specific details about the magnitude of the issue.</t>
@@ -590,7 +633,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -656,13 +699,24 @@
       <family val="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Century Gothic"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -689,9 +743,6 @@
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -710,9 +761,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -722,9 +770,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -732,15 +777,24 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -778,7 +832,7 @@
         <family val="1"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -792,7 +846,7 @@
         <family val="1"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -813,7 +867,7 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -829,7 +883,7 @@
         <family val="1"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -849,7 +903,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -863,7 +917,7 @@
         <family val="1"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -877,7 +931,7 @@
         <family val="1"/>
         <scheme val="major"/>
       </font>
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
       <font>
@@ -918,22 +972,22 @@
       </font>
       <border>
         <left style="thin">
-          <color theme="0" tint="-0.14993743705557422"/>
+          <color theme="0" tint="-0.14990691854609822"/>
         </left>
         <right style="thin">
-          <color theme="0" tint="-0.14993743705557422"/>
+          <color theme="0" tint="-0.14990691854609822"/>
         </right>
         <top style="thin">
-          <color theme="0" tint="-0.14990691854609822"/>
+          <color theme="0" tint="-0.1498764000366222"/>
         </top>
         <bottom style="thick">
           <color theme="1" tint="0.24994659260841701"/>
         </bottom>
         <vertical style="thin">
-          <color theme="0" tint="-0.14993743705557422"/>
+          <color theme="0" tint="-0.14990691854609822"/>
         </vertical>
         <horizontal style="thin">
-          <color theme="0" tint="-0.14990691854609822"/>
+          <color theme="0" tint="-0.1498764000366222"/>
         </horizontal>
       </border>
     </dxf>
@@ -956,13 +1010,15 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ToDo7" displayName="ToDo7" ref="B4:F53" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="B4:F53" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="B4:F53" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Data"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="To Do" dataDxfId="6"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Section" dataDxfId="5"/>
@@ -1177,1120 +1233,1137 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:H77"/>
+  <dimension ref="B1:I77"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="137.5" style="13" customWidth="1"/>
-    <col min="3" max="3" width="21.3984375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="20.19921875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="26.69921875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="38.09765625" style="4" customWidth="1"/>
-    <col min="7" max="8" width="80" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.3984375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="53.19921875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="2.69921875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="8.69921875" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="8.69921875" style="3"/>
+    <col min="1" max="1" width="2.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="108.59765625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="21.3984375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.19921875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="26.69921875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="38.09765625" style="3" customWidth="1"/>
+    <col min="7" max="9" width="80" style="2" customWidth="1"/>
+    <col min="10" max="10" width="53.19921875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="2.69921875" style="2" customWidth="1"/>
+    <col min="12" max="13" width="8.69921875" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="8.69921875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:8" s="5" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="14"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="2:8" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="15" t="s">
+    <row r="1" spans="2:9" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:9" s="4" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="11"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="2:9" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="12" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" s="9" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="10" t="s">
+      <c r="I4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="11" t="s">
+    </row>
+    <row r="5" spans="2:9" s="7" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="18" t="s">
+      <c r="E5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="G5" s="15" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" s="9" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="10" t="s">
+      <c r="H5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1" t="s">
+    </row>
+    <row r="6" spans="2:9" s="7" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="18" t="s">
+      <c r="E6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="G6" s="15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="2:8" s="9" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
+      <c r="H6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1" t="s">
+    </row>
+    <row r="7" spans="2:9" s="7" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="C7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" s="7" customFormat="1" ht="91.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" s="7" customFormat="1" ht="67.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="18" t="s">
+      <c r="E9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" s="7" customFormat="1" ht="56.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" s="7" customFormat="1" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" s="7" customFormat="1" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" s="7" customFormat="1" ht="57" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" s="7" customFormat="1" ht="57" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" s="7" customFormat="1" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="14"/>
+      <c r="G15" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" s="7" customFormat="1" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="14"/>
+      <c r="G16" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" s="7" customFormat="1" ht="42.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="14"/>
+      <c r="G17" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" s="7" customFormat="1" ht="42.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="14"/>
+      <c r="G18" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" s="7" customFormat="1" ht="42.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="14"/>
+      <c r="G19" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" s="7" customFormat="1" ht="42.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" s="9" customFormat="1" ht="91.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="E20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" s="7" customFormat="1" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="14"/>
+      <c r="G21" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" s="7" customFormat="1" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" s="7" customFormat="1" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="14"/>
+      <c r="G23" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" s="7" customFormat="1" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" s="9" customFormat="1" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="E24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="14"/>
+      <c r="G24" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" s="7" customFormat="1" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="14"/>
+      <c r="G25" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" s="7" customFormat="1" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="14"/>
+      <c r="G26" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" s="7" customFormat="1" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" s="7" customFormat="1" ht="77.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" s="7" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="14"/>
+      <c r="G29" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" s="7" customFormat="1" ht="47.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" s="7" customFormat="1" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" s="7" customFormat="1" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="14"/>
+      <c r="G32" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" s="7" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" s="7" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="G34" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" s="7" customFormat="1" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="14"/>
+      <c r="G35" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" s="7" customFormat="1" ht="37.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" s="7" customFormat="1" ht="44.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="14"/>
+      <c r="G37" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" s="7" customFormat="1" ht="44.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" s="7" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="D39" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" s="7" customFormat="1" ht="82.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="G40" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="H40" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" s="7" customFormat="1" ht="82.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="G41" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="I41" s="18" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" s="7" customFormat="1" ht="82.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" s="9" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="E42" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="H42" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="I42" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" s="7" customFormat="1" ht="82.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F43" s="14"/>
+      <c r="G43" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="H43" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="I43" s="18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" s="7" customFormat="1" ht="82.8" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="14"/>
+      <c r="G44" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="H44" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" s="7" customFormat="1" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" s="7" customFormat="1" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" s="9" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="E46" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="G46" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="H46" s="15" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" s="7" customFormat="1" ht="59.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D47" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" s="9" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="E47" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="G47" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="H47" s="15" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" s="7" customFormat="1" ht="77.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G48" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="H48" s="15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" s="7" customFormat="1" ht="54.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="G49" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" s="7" customFormat="1" ht="58.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" s="9" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" s="9" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="16"/>
-      <c r="G14" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" s="9" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="16"/>
-      <c r="G15" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" s="9" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="18" t="s">
+      <c r="E50" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="14"/>
+      <c r="G50" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="15" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" s="7" customFormat="1" ht="63" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" s="9" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" s="9" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" s="9" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" s="9" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" s="9" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" s="9" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" s="9" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="16"/>
-      <c r="G23" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" s="9" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" s="9" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="H25" s="18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" s="9" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" s="9" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="H27" s="18" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" s="9" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" s="9" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="H30" s="18" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" s="9" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="H31" s="18" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" s="9" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" s="9" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="H33" s="18" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" s="9" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="16"/>
-      <c r="G34" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" s="9" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="16"/>
-      <c r="G35" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" s="9" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G36" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="H36" s="18" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" s="9" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="H37" s="18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" s="9" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" s="9" customFormat="1" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="H39" s="18" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" s="9" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="H40" s="18" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" s="9" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="H41" s="18" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" s="9" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="H42" s="18" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" s="9" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="H43" s="18" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" s="9" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="16"/>
-      <c r="G44" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="H44" s="18" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" s="9" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="G45" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="H45" s="18" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" s="9" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="G46" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="H46" s="18" t="s">
+      <c r="E51" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="14"/>
+      <c r="G51" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="H51" s="15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" s="7" customFormat="1" ht="77.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C52" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="47" spans="2:8" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="10" t="s">
+      <c r="D52" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C47" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="G47" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="H47" s="18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" s="9" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G48" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="H48" s="18" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" s="9" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="G49" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="H49" s="18" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" s="9" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="16"/>
-      <c r="G50" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="H50" s="18" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" s="9" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="16"/>
-      <c r="G51" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="H51" s="18" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" s="9" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="G52" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="H52" s="18" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" s="9" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="16"/>
-      <c r="G53" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="H53" s="18" t="s">
-        <v>187</v>
+      <c r="E52" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="G52" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="H52" s="15" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" s="7" customFormat="1" ht="77.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="14"/>
+      <c r="G53" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="H53" s="15" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="2:8" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
